--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70A5AEF-86C4-4102-BC0D-61F50DCEA050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B240ABF8-0D52-4707-90E3-5552C1CE5A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -849,10 +849,10 @@
         <v>7</v>
       </c>
       <c r="E10" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="10">
         <v>228215</v>
@@ -1142,19 +1142,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="10">
         <v>7</v>
       </c>
       <c r="E23" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="10">
         <v>13</v>
       </c>
       <c r="G23" s="10">
-        <v>56280</v>
+        <v>57361</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1164,7 +1164,7 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>2131895</v>
+        <v>2132976</v>
       </c>
     </row>
   </sheetData>
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1281,7 +1281,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D4" s="10">
         <v>14</v>
@@ -1290,10 +1290,10 @@
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G4" s="10">
-        <v>470477</v>
+        <v>471763</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1307,16 +1307,16 @@
         <v>51</v>
       </c>
       <c r="D5" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="10">
         <v>19</v>
       </c>
       <c r="F5" s="10">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G5" s="10">
-        <v>754141</v>
+        <v>794356</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G6" s="10">
         <v>75847</v>
@@ -1350,7 +1350,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D7" s="10">
         <v>22</v>
@@ -1359,10 +1359,10 @@
         <v>19</v>
       </c>
       <c r="F7" s="10">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G7" s="10">
-        <v>3155314</v>
+        <v>3184319</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,7 +1373,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D8" s="10">
         <v>19</v>
@@ -1382,10 +1382,10 @@
         <v>27</v>
       </c>
       <c r="F8" s="10">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G8" s="10">
-        <v>1178542</v>
+        <v>1184020</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1419,7 +1419,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="10">
         <v>21</v>
@@ -1428,10 +1428,10 @@
         <v>25</v>
       </c>
       <c r="F10" s="10">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G10" s="10">
-        <v>876808</v>
+        <v>902315</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1442,19 +1442,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D11" s="10">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" s="10">
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G11" s="10">
-        <v>5310709</v>
+        <v>5351505</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,19 +1465,19 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D12" s="10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" s="10">
         <v>19</v>
       </c>
       <c r="F12" s="10">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G12" s="10">
-        <v>2057858</v>
+        <v>2074232</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1488,19 +1488,19 @@
         <v>31</v>
       </c>
       <c r="C13" s="10">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" s="10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E13" s="10">
         <v>21</v>
       </c>
       <c r="F13" s="10">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G13" s="10">
-        <v>1183123</v>
+        <v>1214718</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,7 +1511,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D14" s="10">
         <v>36</v>
@@ -1520,10 +1520,10 @@
         <v>14</v>
       </c>
       <c r="F14" s="10">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G14" s="10">
-        <v>651378</v>
+        <v>651903</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,7 +1534,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D15" s="10">
         <v>27</v>
@@ -1543,10 +1543,10 @@
         <v>14</v>
       </c>
       <c r="F15" s="10">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G15" s="10">
-        <v>1074477</v>
+        <v>1079334</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1557,7 +1557,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="10">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D16" s="10">
         <v>18</v>
@@ -1566,10 +1566,10 @@
         <v>18</v>
       </c>
       <c r="F16" s="10">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G16" s="10">
-        <v>1372284</v>
+        <v>1382279</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1580,19 +1580,19 @@
         <v>31</v>
       </c>
       <c r="C17" s="10">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D17" s="10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E17" s="10">
         <v>26</v>
       </c>
       <c r="F17" s="10">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G17" s="10">
-        <v>4126436</v>
+        <v>4233577</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1603,7 +1603,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="10">
         <v>4</v>
@@ -1612,10 +1612,10 @@
         <v>18</v>
       </c>
       <c r="F18" s="10">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="10">
-        <v>313340</v>
+        <v>314213</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,7 +1626,7 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D19" s="10">
         <v>12</v>
@@ -1635,10 +1635,10 @@
         <v>15</v>
       </c>
       <c r="F19" s="10">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G19" s="10">
-        <v>797083</v>
+        <v>798452</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1649,7 +1649,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="10">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D20" s="10">
         <v>2</v>
@@ -1658,10 +1658,10 @@
         <v>24</v>
       </c>
       <c r="F20" s="10">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G20" s="10">
-        <v>178017</v>
+        <v>178619</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,7 +1672,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D21" s="10">
         <v>22</v>
@@ -1681,10 +1681,10 @@
         <v>12</v>
       </c>
       <c r="F21" s="10">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G21" s="10">
-        <v>1148249</v>
+        <v>1149698</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D22" s="10">
         <v>29</v>
@@ -1704,10 +1704,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="10">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G22" s="10">
-        <v>1291818</v>
+        <v>1300252</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1718,7 +1718,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D23" s="10">
         <v>15</v>
@@ -1727,10 +1727,10 @@
         <v>15</v>
       </c>
       <c r="F23" s="10">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G23" s="10">
-        <v>329937</v>
+        <v>338818</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,11 +1740,11 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4530</v>
+        <v>4557</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
@@ -1752,11 +1752,11 @@
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5315</v>
+        <v>5345</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>26795494</v>
+        <v>27129876</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B240ABF8-0D52-4707-90E3-5552C1CE5A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00749B7-3346-4A36-8A5A-C84C315F28DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1258,7 +1258,7 @@
         <v>31</v>
       </c>
       <c r="C3" s="10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="10">
         <v>6</v>
@@ -1267,10 +1267,10 @@
         <v>21</v>
       </c>
       <c r="F3" s="10">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G3" s="10">
-        <v>387574</v>
+        <v>387683</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1284,16 +1284,16 @@
         <v>279</v>
       </c>
       <c r="D4" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="10">
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G4" s="10">
-        <v>471763</v>
+        <v>474382</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1304,10 +1304,10 @@
         <v>31</v>
       </c>
       <c r="C5" s="10">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" s="10">
         <v>19</v>
@@ -1316,7 +1316,7 @@
         <v>82</v>
       </c>
       <c r="G5" s="10">
-        <v>794356</v>
+        <v>799024</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1385,7 +1385,7 @@
         <v>294</v>
       </c>
       <c r="G8" s="10">
-        <v>1184020</v>
+        <v>1184458</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1431,7 +1431,7 @@
         <v>128</v>
       </c>
       <c r="G10" s="10">
-        <v>902315</v>
+        <v>909219</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1454,7 +1454,7 @@
         <v>397</v>
       </c>
       <c r="G11" s="10">
-        <v>5351505</v>
+        <v>5352405</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1468,16 +1468,16 @@
         <v>294</v>
       </c>
       <c r="D12" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="10">
         <v>19</v>
       </c>
       <c r="F12" s="10">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G12" s="10">
-        <v>2074232</v>
+        <v>2091507</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1494,10 +1494,10 @@
         <v>41</v>
       </c>
       <c r="E13" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="10">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G13" s="10">
         <v>1214718</v>
@@ -1511,10 +1511,10 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D14" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" s="10">
         <v>14</v>
@@ -1523,7 +1523,7 @@
         <v>494</v>
       </c>
       <c r="G14" s="10">
-        <v>651903</v>
+        <v>652528</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1569,7 +1569,7 @@
         <v>291</v>
       </c>
       <c r="G16" s="10">
-        <v>1382279</v>
+        <v>1385280</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>281</v>
       </c>
       <c r="G17" s="10">
-        <v>4233577</v>
+        <v>4282440</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1603,19 +1603,19 @@
         <v>31</v>
       </c>
       <c r="C18" s="10">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="10">
         <v>18</v>
       </c>
       <c r="F18" s="10">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" s="10">
-        <v>314213</v>
+        <v>337120</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,7 +1626,7 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D19" s="10">
         <v>12</v>
@@ -1635,10 +1635,10 @@
         <v>15</v>
       </c>
       <c r="F19" s="10">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G19" s="10">
-        <v>798452</v>
+        <v>800398</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1649,19 +1649,19 @@
         <v>31</v>
       </c>
       <c r="C20" s="10">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="10">
         <v>2</v>
       </c>
       <c r="E20" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F20" s="10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G20" s="10">
-        <v>178619</v>
+        <v>178694</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,19 +1672,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D21" s="10">
         <v>22</v>
       </c>
       <c r="E21" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="10">
         <v>447</v>
       </c>
       <c r="G21" s="10">
-        <v>1149698</v>
+        <v>1153859</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D22" s="10">
         <v>29</v>
@@ -1704,10 +1704,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="10">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G22" s="10">
-        <v>1300252</v>
+        <v>1306522</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1724,10 +1724,10 @@
         <v>15</v>
       </c>
       <c r="E23" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23" s="10">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G23" s="10">
         <v>338818</v>
@@ -1740,7 +1740,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4557</v>
+        <v>4566</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
@@ -1748,15 +1748,15 @@
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5345</v>
+        <v>5356</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>27129876</v>
+        <v>27250637</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00749B7-3346-4A36-8A5A-C84C315F28DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD59E3D7-34A7-4363-B375-FA657C198F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1281,19 +1281,19 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D4" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="10">
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G4" s="10">
-        <v>474382</v>
+        <v>482452</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1350,7 +1350,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D7" s="10">
         <v>22</v>
@@ -1359,10 +1359,10 @@
         <v>19</v>
       </c>
       <c r="F7" s="10">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G7" s="10">
-        <v>3184319</v>
+        <v>3188702</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,10 +1373,10 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D8" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="10">
         <v>27</v>
@@ -1385,7 +1385,7 @@
         <v>294</v>
       </c>
       <c r="G8" s="10">
-        <v>1184458</v>
+        <v>1185384</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1425,13 +1425,13 @@
         <v>21</v>
       </c>
       <c r="E10" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="10">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G10" s="10">
-        <v>909219</v>
+        <v>909375</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1488,19 +1488,19 @@
         <v>31</v>
       </c>
       <c r="C13" s="10">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" s="10">
         <v>41</v>
       </c>
       <c r="E13" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" s="10">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G13" s="10">
-        <v>1214718</v>
+        <v>1229539</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1517,10 +1517,10 @@
         <v>35</v>
       </c>
       <c r="E14" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F14" s="10">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G14" s="10">
         <v>652528</v>
@@ -1560,16 +1560,16 @@
         <v>255</v>
       </c>
       <c r="D16" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" s="10">
         <v>18</v>
       </c>
       <c r="F16" s="10">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G16" s="10">
-        <v>1385280</v>
+        <v>1388037</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1580,10 +1580,10 @@
         <v>31</v>
       </c>
       <c r="C17" s="10">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D17" s="10">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="10">
         <v>26</v>
@@ -1592,7 +1592,7 @@
         <v>281</v>
       </c>
       <c r="G17" s="10">
-        <v>4282440</v>
+        <v>4286139</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1603,10 +1603,10 @@
         <v>31</v>
       </c>
       <c r="C18" s="10">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="10">
         <v>18</v>
@@ -1615,7 +1615,7 @@
         <v>79</v>
       </c>
       <c r="G18" s="10">
-        <v>337120</v>
+        <v>339647</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,7 +1626,7 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D19" s="10">
         <v>12</v>
@@ -1635,10 +1635,10 @@
         <v>15</v>
       </c>
       <c r="F19" s="10">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G19" s="10">
-        <v>800398</v>
+        <v>802582</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1718,19 +1718,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" s="10">
         <v>15</v>
       </c>
       <c r="E23" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F23" s="10">
         <v>129</v>
       </c>
       <c r="G23" s="10">
-        <v>338818</v>
+        <v>340003</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4566</v>
+        <v>4575</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5356</v>
+        <v>5364</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>27250637</v>
+        <v>27291345</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD59E3D7-34A7-4363-B375-FA657C198F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE89FC0F-8CD6-44BE-9AF1-A85C183FCB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G6" s="10">
-        <v>75847</v>
+        <v>76516</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1353,16 +1353,16 @@
         <v>289</v>
       </c>
       <c r="D7" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="10">
         <v>19</v>
       </c>
       <c r="F7" s="10">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G7" s="10">
-        <v>3188702</v>
+        <v>3201949</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,7 +1373,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D8" s="10">
         <v>18</v>
@@ -1382,10 +1382,10 @@
         <v>27</v>
       </c>
       <c r="F8" s="10">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G8" s="10">
-        <v>1185384</v>
+        <v>1197641</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1422,16 +1422,16 @@
         <v>82</v>
       </c>
       <c r="D10" s="10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" s="10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="10">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G10" s="10">
-        <v>909375</v>
+        <v>934435</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1445,16 +1445,16 @@
         <v>330</v>
       </c>
       <c r="D11" s="10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="10">
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G11" s="10">
-        <v>5352405</v>
+        <v>5365580</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,7 +1511,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D14" s="10">
         <v>35</v>
@@ -1520,10 +1520,10 @@
         <v>15</v>
       </c>
       <c r="F14" s="10">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G14" s="10">
-        <v>652528</v>
+        <v>653078</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,7 +1534,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D15" s="10">
         <v>27</v>
@@ -1543,10 +1543,10 @@
         <v>14</v>
       </c>
       <c r="F15" s="10">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G15" s="10">
-        <v>1079334</v>
+        <v>1080308</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>281</v>
       </c>
       <c r="G17" s="10">
-        <v>4286139</v>
+        <v>4296060</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,7 +1672,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D21" s="10">
         <v>22</v>
@@ -1681,10 +1681,10 @@
         <v>11</v>
       </c>
       <c r="F21" s="10">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G21" s="10">
-        <v>1153859</v>
+        <v>1156272</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1718,7 +1718,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D23" s="10">
         <v>15</v>
@@ -1727,10 +1727,10 @@
         <v>15</v>
       </c>
       <c r="F23" s="10">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G23" s="10">
-        <v>340003</v>
+        <v>342876</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4575</v>
+        <v>4583</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5364</v>
+        <v>5378</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>27291345</v>
+        <v>27372484</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE89FC0F-8CD6-44BE-9AF1-A85C183FCB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771B492E-706D-4408-8585-858DD7A17D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -1261,16 +1261,16 @@
         <v>59</v>
       </c>
       <c r="D3" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="10">
         <v>21</v>
       </c>
       <c r="F3" s="10">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G3" s="10">
-        <v>387683</v>
+        <v>395492</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1281,7 +1281,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D4" s="10">
         <v>14</v>
@@ -1290,10 +1290,10 @@
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G4" s="10">
-        <v>482452</v>
+        <v>482947</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1350,10 +1350,10 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D7" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="10">
         <v>19</v>
@@ -1362,7 +1362,7 @@
         <v>331</v>
       </c>
       <c r="G7" s="10">
-        <v>3201949</v>
+        <v>3204300</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1431,7 +1431,7 @@
         <v>132</v>
       </c>
       <c r="G10" s="10">
-        <v>934435</v>
+        <v>964904</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1442,10 +1442,10 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D11" s="10">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="10">
         <v>21</v>
@@ -1454,7 +1454,7 @@
         <v>399</v>
       </c>
       <c r="G11" s="10">
-        <v>5365580</v>
+        <v>5365877</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,7 +1465,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D12" s="10">
         <v>31</v>
@@ -1474,10 +1474,10 @@
         <v>19</v>
       </c>
       <c r="F12" s="10">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G12" s="10">
-        <v>2091507</v>
+        <v>2099516</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1560,16 +1560,16 @@
         <v>255</v>
       </c>
       <c r="D16" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" s="10">
         <v>18</v>
       </c>
       <c r="F16" s="10">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G16" s="10">
-        <v>1388037</v>
+        <v>1389844</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1583,16 +1583,16 @@
         <v>218</v>
       </c>
       <c r="D17" s="10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17" s="10">
         <v>26</v>
       </c>
       <c r="F17" s="10">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G17" s="10">
-        <v>4296060</v>
+        <v>4302363</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,7 +1626,7 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D19" s="10">
         <v>12</v>
@@ -1635,10 +1635,10 @@
         <v>15</v>
       </c>
       <c r="F19" s="10">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G19" s="10">
-        <v>802582</v>
+        <v>804711</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D22" s="10">
         <v>29</v>
@@ -1704,10 +1704,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="10">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G22" s="10">
-        <v>1306522</v>
+        <v>1309844</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,11 +1740,11 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4583</v>
+        <v>4589</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
@@ -1752,11 +1752,11 @@
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5378</v>
+        <v>5385</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>27372484</v>
+        <v>27435475</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771B492E-706D-4408-8585-858DD7A17D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0604E0E7-5698-40A9-8387-0FEF71DAF5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1258,10 +1258,10 @@
         <v>31</v>
       </c>
       <c r="C3" s="10">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="10">
         <v>21</v>
@@ -1270,7 +1270,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="10">
-        <v>395492</v>
+        <v>401360</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1419,10 +1419,10 @@
         <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" s="10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="10">
         <v>25</v>
@@ -1431,7 +1431,7 @@
         <v>132</v>
       </c>
       <c r="G10" s="10">
-        <v>964904</v>
+        <v>978222</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1454,7 +1454,7 @@
         <v>399</v>
       </c>
       <c r="G11" s="10">
-        <v>5365877</v>
+        <v>5375866</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>282</v>
       </c>
       <c r="G17" s="10">
-        <v>4302363</v>
+        <v>4304501</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1649,7 +1649,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="10">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D20" s="10">
         <v>2</v>
@@ -1658,10 +1658,10 @@
         <v>25</v>
       </c>
       <c r="F20" s="10">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G20" s="10">
-        <v>178694</v>
+        <v>182773</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,11 +1740,11 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4589</v>
+        <v>4592</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
@@ -1752,11 +1752,11 @@
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5385</v>
+        <v>5386</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>27435475</v>
+        <v>27470867</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0604E0E7-5698-40A9-8387-0FEF71DAF5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B96EAC1-376C-4B70-A0F6-1C21BAAAF6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1376,16 +1376,16 @@
         <v>250</v>
       </c>
       <c r="D8" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="10">
         <v>27</v>
       </c>
       <c r="F8" s="10">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G8" s="10">
-        <v>1197641</v>
+        <v>1210263</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1422,16 +1422,16 @@
         <v>83</v>
       </c>
       <c r="D10" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="10">
         <v>25</v>
       </c>
       <c r="F10" s="10">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G10" s="10">
-        <v>978222</v>
+        <v>992674</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1442,7 +1442,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D11" s="10">
         <v>47</v>
@@ -1451,10 +1451,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G11" s="10">
-        <v>5375866</v>
+        <v>5377154</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,7 +1465,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D12" s="10">
         <v>31</v>
@@ -1474,10 +1474,10 @@
         <v>19</v>
       </c>
       <c r="F12" s="10">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G12" s="10">
-        <v>2099516</v>
+        <v>2109968</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1488,19 +1488,19 @@
         <v>31</v>
       </c>
       <c r="C13" s="10">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" s="10">
         <v>41</v>
       </c>
       <c r="E13" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" s="10">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G13" s="10">
-        <v>1229539</v>
+        <v>1232079</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>282</v>
       </c>
       <c r="G17" s="10">
-        <v>4304501</v>
+        <v>4305702</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1661,7 +1661,7 @@
         <v>99</v>
       </c>
       <c r="G20" s="10">
-        <v>182773</v>
+        <v>183270</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D22" s="10">
         <v>29</v>
@@ -1704,10 +1704,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="10">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G22" s="10">
-        <v>1309844</v>
+        <v>1316259</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4592</v>
+        <v>4599</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5386</v>
+        <v>5396</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>27470867</v>
+        <v>27520334</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B96EAC1-376C-4B70-A0F6-1C21BAAAF6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE23B929-9D3B-4E61-8280-0D814603F0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1122,16 +1122,16 @@
         <v>9</v>
       </c>
       <c r="D22" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="10">
         <v>3</v>
       </c>
       <c r="F22" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="10">
-        <v>158154</v>
+        <v>159656</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>2132976</v>
+        <v>2134478</v>
       </c>
     </row>
   </sheetData>
@@ -1379,13 +1379,13 @@
         <v>19</v>
       </c>
       <c r="E8" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="10">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G8" s="10">
-        <v>1210263</v>
+        <v>1214629</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1419,7 +1419,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" s="10">
         <v>25</v>
@@ -1428,10 +1428,10 @@
         <v>25</v>
       </c>
       <c r="F10" s="10">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G10" s="10">
-        <v>992674</v>
+        <v>996998</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1583,16 +1583,16 @@
         <v>218</v>
       </c>
       <c r="D17" s="10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E17" s="10">
         <v>26</v>
       </c>
       <c r="F17" s="10">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G17" s="10">
-        <v>4305702</v>
+        <v>4311504</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1661,7 +1661,7 @@
         <v>99</v>
       </c>
       <c r="G20" s="10">
-        <v>183270</v>
+        <v>185269</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4599</v>
+        <v>4600</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5396</v>
+        <v>5400</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>27520334</v>
+        <v>27536825</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE23B929-9D3B-4E61-8280-0D814603F0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90177F49-5976-4F0E-A59A-51BE1B0E27F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -984,16 +984,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="10">
         <v>1</v>
       </c>
       <c r="F16" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="10">
-        <v>62127</v>
+        <v>63562</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>2134478</v>
+        <v>2135913</v>
       </c>
     </row>
   </sheetData>
@@ -1281,7 +1281,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D4" s="10">
         <v>14</v>
@@ -1290,10 +1290,10 @@
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G4" s="10">
-        <v>482947</v>
+        <v>483219</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G6" s="10">
-        <v>76516</v>
+        <v>77117</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1350,7 +1350,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D7" s="10">
         <v>22</v>
@@ -1359,10 +1359,10 @@
         <v>19</v>
       </c>
       <c r="F7" s="10">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G7" s="10">
-        <v>3204300</v>
+        <v>3205548</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,19 +1373,19 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D8" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="10">
         <v>28</v>
       </c>
       <c r="F8" s="10">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G8" s="10">
-        <v>1214629</v>
+        <v>1223476</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1425,13 +1425,13 @@
         <v>25</v>
       </c>
       <c r="E10" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="10">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G10" s="10">
-        <v>996998</v>
+        <v>997598</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1442,7 +1442,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D11" s="10">
         <v>47</v>
@@ -1451,10 +1451,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G11" s="10">
-        <v>5377154</v>
+        <v>5377992</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,7 +1465,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D12" s="10">
         <v>31</v>
@@ -1474,10 +1474,10 @@
         <v>19</v>
       </c>
       <c r="F12" s="10">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G12" s="10">
-        <v>2109968</v>
+        <v>2110602</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,19 +1511,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D14" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="10">
         <v>15</v>
       </c>
       <c r="F14" s="10">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G14" s="10">
-        <v>653078</v>
+        <v>655668</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,19 +1534,19 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D15" s="10">
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15" s="10">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G15" s="10">
-        <v>1080308</v>
+        <v>1083146</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1557,7 +1557,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="10">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D16" s="10">
         <v>20</v>
@@ -1566,10 +1566,10 @@
         <v>18</v>
       </c>
       <c r="F16" s="10">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G16" s="10">
-        <v>1389844</v>
+        <v>1390078</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1580,7 +1580,7 @@
         <v>31</v>
       </c>
       <c r="C17" s="10">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D17" s="10">
         <v>40</v>
@@ -1589,10 +1589,10 @@
         <v>26</v>
       </c>
       <c r="F17" s="10">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G17" s="10">
-        <v>4311504</v>
+        <v>4312636</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1606,16 +1606,16 @@
         <v>57</v>
       </c>
       <c r="D18" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="10">
         <v>18</v>
       </c>
       <c r="F18" s="10">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G18" s="10">
-        <v>339647</v>
+        <v>347303</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,7 +1626,7 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D19" s="10">
         <v>12</v>
@@ -1635,10 +1635,10 @@
         <v>15</v>
       </c>
       <c r="F19" s="10">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G19" s="10">
-        <v>804711</v>
+        <v>806637</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,7 +1672,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D21" s="10">
         <v>22</v>
@@ -1681,10 +1681,10 @@
         <v>11</v>
       </c>
       <c r="F21" s="10">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G21" s="10">
-        <v>1156272</v>
+        <v>1159601</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D22" s="10">
         <v>29</v>
@@ -1704,10 +1704,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="10">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G22" s="10">
-        <v>1316259</v>
+        <v>1326409</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1718,7 +1718,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="10">
         <v>15</v>
@@ -1727,10 +1727,10 @@
         <v>15</v>
       </c>
       <c r="F23" s="10">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G23" s="10">
-        <v>342876</v>
+        <v>346341</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,11 +1740,11 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4600</v>
+        <v>4619</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
@@ -1752,11 +1752,11 @@
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5400</v>
+        <v>5420</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>27536825</v>
+        <v>27583185</v>
       </c>
     </row>
   </sheetData>
